--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE33C586-3C83-48AF-B33D-B2AEF6035173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FBBCA5-F987-4B3B-8926-AFDC49A01FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6743CD84-9FDB-4CBE-AD45-AEEEA894EE36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C1EA7A-3DD2-4EFB-857F-EC304B5960BC}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FBBCA5-F987-4B3B-8926-AFDC49A01FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5BA3263-0157-4417-BDF4-22FAF6EEEEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C1EA7A-3DD2-4EFB-857F-EC304B5960BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99657A21-416A-4E9C-AC4B-4F5BF50882F1}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5BA3263-0157-4417-BDF4-22FAF6EEEEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D717F03B-5BEF-4A91-BDD9-42CA8A029183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99657A21-416A-4E9C-AC4B-4F5BF50882F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB03C1DC-4E3D-4776-96E6-29AB18FFFE42}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D717F03B-5BEF-4A91-BDD9-42CA8A029183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BD5AD4-2B0D-426A-840A-0F57E7E326E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB03C1DC-4E3D-4776-96E6-29AB18FFFE42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B73037B3-4B95-418B-8B5E-21D8D209B97F}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BD5AD4-2B0D-426A-840A-0F57E7E326E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC537E01-0841-44F6-846B-0CA96150F85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B73037B3-4B95-418B-8B5E-21D8D209B97F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3A70BB-1D85-49E4-ACE4-89398CABFDAF}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC537E01-0841-44F6-846B-0CA96150F85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D024BFC-986A-48F1-836F-B535BD8B3D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3A70BB-1D85-49E4-ACE4-89398CABFDAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC48AC0-C491-4022-986E-BCA44C42E43C}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D024BFC-986A-48F1-836F-B535BD8B3D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5F2D397-BF3D-492F-BB47-98180CDBEA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC48AC0-C491-4022-986E-BCA44C42E43C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20403F8-4814-4151-9B2F-9C4A366280AD}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5F2D397-BF3D-492F-BB47-98180CDBEA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45FEFCD5-AA69-4BE9-8BAA-F5F71F45DCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20403F8-4814-4151-9B2F-9C4A366280AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C223A88C-3A52-4472-9B72-80C45667567A}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45FEFCD5-AA69-4BE9-8BAA-F5F71F45DCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1F7896-0EA1-4FD5-8E1F-183C72B52AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C223A88C-3A52-4472-9B72-80C45667567A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C483DA3-949D-4901-9EE1-721FB3FC550C}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1F7896-0EA1-4FD5-8E1F-183C72B52AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A9F04D9-88B8-49DF-BBDA-3B4551CBEEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,7 +2047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C483DA3-949D-4901-9EE1-721FB3FC550C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16B2F92-9FF7-4F21-9770-65C55DDA5746}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A9F04D9-88B8-49DF-BBDA-3B4551CBEEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5984F0A2-A93D-4A64-AE9B-30F7E5B6E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,6 +41,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -98,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="489">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -359,6 +385,9 @@
   </si>
   <si>
     <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -2047,7 +2076,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16B2F92-9FF7-4F21-9770-65C55DDA5746}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D611C2-F6F4-45B3-B13B-165722A91E97}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2056,13 +2085,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="U2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.45">
@@ -2070,25 +2099,25 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L3" t="s">
         <v>14</v>
@@ -2097,30 +2126,30 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="U3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="V3" t="s">
         <v>3</v>
       </c>
       <c r="W3" t="s">
+        <v>253</v>
+      </c>
+      <c r="X3" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA3" t="s">
         <v>252</v>
-      </c>
-      <c r="X3" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="4" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4">
         <v>0.49155601918804742</v>
@@ -2132,60 +2161,60 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J4">
         <v>6.4746879831177079E-2</v>
       </c>
       <c r="K4" t="s">
+        <v>258</v>
+      </c>
+      <c r="L4" t="s">
         <v>257</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4" t="s">
         <v>256</v>
       </c>
-      <c r="P4" t="s">
-        <v>255</v>
-      </c>
       <c r="Q4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AB4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AC4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AD4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AE4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>0.98311203837609484</v>
@@ -2197,46 +2226,46 @@
         <v>0.99561999999999995</v>
       </c>
       <c r="H5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J5">
         <v>6.120396201617069E-2</v>
       </c>
       <c r="K5" t="s">
+        <v>258</v>
+      </c>
+      <c r="L5" t="s">
         <v>257</v>
       </c>
-      <c r="L5" t="s">
-        <v>256</v>
-      </c>
       <c r="P5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q5" t="s">
+        <v>302</v>
+      </c>
+      <c r="R5" t="s">
         <v>301</v>
       </c>
-      <c r="R5" t="s">
-        <v>300</v>
-      </c>
       <c r="U5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V5" t="s">
+        <v>315</v>
+      </c>
+      <c r="W5" t="s">
+        <v>313</v>
+      </c>
+      <c r="X5" t="s">
         <v>314</v>
       </c>
-      <c r="W5" t="s">
-        <v>312</v>
-      </c>
-      <c r="X5" t="s">
-        <v>313</v>
-      </c>
       <c r="AA5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AB5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2245,12 +2274,12 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>0.49155601918804742</v>
@@ -2262,45 +2291,45 @@
         <v>0.99994000000000005</v>
       </c>
       <c r="H6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J6">
         <v>7.0125316451925546E-2</v>
       </c>
       <c r="K6" t="s">
+        <v>258</v>
+      </c>
+      <c r="L6" t="s">
         <v>257</v>
       </c>
-      <c r="L6" t="s">
-        <v>256</v>
-      </c>
       <c r="P6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="W6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7">
         <v>0.98311203837609484</v>
@@ -2312,45 +2341,45 @@
         <v>0.99334</v>
       </c>
       <c r="H7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J7">
         <v>0.12429242027926862</v>
       </c>
       <c r="K7" t="s">
+        <v>258</v>
+      </c>
+      <c r="L7" t="s">
         <v>257</v>
       </c>
-      <c r="L7" t="s">
-        <v>256</v>
-      </c>
       <c r="P7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="W7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>0.49155601918804742</v>
@@ -2362,45 +2391,45 @@
         <v>0.99994000000000005</v>
       </c>
       <c r="H8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J8">
         <v>4.9074747359742522E-2</v>
       </c>
       <c r="K8" t="s">
+        <v>258</v>
+      </c>
+      <c r="L8" t="s">
         <v>257</v>
       </c>
-      <c r="L8" t="s">
-        <v>256</v>
-      </c>
       <c r="P8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9">
         <v>0.49155601918804742</v>
@@ -2412,45 +2441,45 @@
         <v>0.99646000000000001</v>
       </c>
       <c r="H9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J9">
         <v>2.4727445074139667E-2</v>
       </c>
       <c r="K9" t="s">
+        <v>258</v>
+      </c>
+      <c r="L9" t="s">
         <v>257</v>
       </c>
-      <c r="L9" t="s">
-        <v>256</v>
-      </c>
       <c r="P9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10">
         <v>0.49155601918804742</v>
@@ -2462,45 +2491,45 @@
         <v>0.99951999999999996</v>
       </c>
       <c r="H10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J10">
         <v>2.3624966116599904E-2</v>
       </c>
       <c r="K10" t="s">
+        <v>258</v>
+      </c>
+      <c r="L10" t="s">
         <v>257</v>
       </c>
-      <c r="L10" t="s">
-        <v>256</v>
-      </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="W10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11">
         <v>0.49155601918804742</v>
@@ -2512,45 +2541,45 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="H11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J11">
         <v>0.47683269063818606</v>
       </c>
       <c r="K11" t="s">
+        <v>258</v>
+      </c>
+      <c r="L11" t="s">
         <v>257</v>
       </c>
-      <c r="L11" t="s">
-        <v>256</v>
-      </c>
       <c r="P11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12">
         <v>0.98311203837609484</v>
@@ -2562,45 +2591,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J12">
         <v>6.6688786721083068E-2</v>
       </c>
       <c r="K12" t="s">
+        <v>258</v>
+      </c>
+      <c r="L12" t="s">
         <v>257</v>
       </c>
-      <c r="L12" t="s">
-        <v>256</v>
-      </c>
       <c r="P12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="W12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13">
         <v>0.98311203837609484</v>
@@ -2612,45 +2641,45 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="H13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J13">
         <v>1.8682785511706303E-2</v>
       </c>
       <c r="K13" t="s">
+        <v>258</v>
+      </c>
+      <c r="L13" t="s">
         <v>257</v>
       </c>
-      <c r="L13" t="s">
-        <v>256</v>
-      </c>
       <c r="P13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="W13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14">
         <v>0.49155601918804742</v>
@@ -2662,45 +2691,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J14">
         <v>6.4746879831177079E-2</v>
       </c>
       <c r="K14" t="s">
+        <v>258</v>
+      </c>
+      <c r="L14" t="s">
         <v>257</v>
       </c>
-      <c r="L14" t="s">
-        <v>256</v>
-      </c>
       <c r="P14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="W14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C15">
         <v>0.98311203837609484</v>
@@ -2712,45 +2741,45 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="H15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J15">
         <v>6.120396201617069E-2</v>
       </c>
       <c r="K15" t="s">
+        <v>258</v>
+      </c>
+      <c r="L15" t="s">
         <v>257</v>
       </c>
-      <c r="L15" t="s">
-        <v>256</v>
-      </c>
       <c r="P15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q15" t="s">
+        <v>302</v>
+      </c>
+      <c r="R15" t="s">
         <v>301</v>
       </c>
-      <c r="R15" t="s">
-        <v>300</v>
-      </c>
       <c r="U15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="W15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16">
         <v>0.98311203837609484</v>
@@ -2762,45 +2791,45 @@
         <v>0.99939999999999996</v>
       </c>
       <c r="H16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J16">
         <v>7.0125316451925546E-2</v>
       </c>
       <c r="K16" t="s">
+        <v>258</v>
+      </c>
+      <c r="L16" t="s">
         <v>257</v>
       </c>
-      <c r="L16" t="s">
-        <v>256</v>
-      </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="W16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17">
         <v>0.49155601918804742</v>
@@ -2812,45 +2841,45 @@
         <v>0.98631999999999997</v>
       </c>
       <c r="H17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J17">
         <v>0.12429242027926862</v>
       </c>
       <c r="K17" t="s">
+        <v>258</v>
+      </c>
+      <c r="L17" t="s">
         <v>257</v>
       </c>
-      <c r="L17" t="s">
-        <v>256</v>
-      </c>
       <c r="P17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="W17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18">
         <v>0.49155601918804742</v>
@@ -2862,45 +2891,45 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="H18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J18">
         <v>4.9074747359742522E-2</v>
       </c>
       <c r="K18" t="s">
+        <v>258</v>
+      </c>
+      <c r="L18" t="s">
         <v>257</v>
       </c>
-      <c r="L18" t="s">
-        <v>256</v>
-      </c>
       <c r="P18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V18" t="s">
+        <v>329</v>
+      </c>
+      <c r="W18" t="s">
         <v>328</v>
       </c>
-      <c r="W18" t="s">
-        <v>327</v>
-      </c>
       <c r="X18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19">
         <v>0.49155601918804742</v>
@@ -2912,45 +2941,45 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="H19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J19">
         <v>2.4727445074139667E-2</v>
       </c>
       <c r="K19" t="s">
+        <v>258</v>
+      </c>
+      <c r="L19" t="s">
         <v>257</v>
       </c>
-      <c r="L19" t="s">
-        <v>256</v>
-      </c>
       <c r="P19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="W19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20">
         <v>0.98311203837609484</v>
@@ -2962,45 +2991,45 @@
         <v>0.99790000000000001</v>
       </c>
       <c r="H20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J20">
         <v>2.3624966116599904E-2</v>
       </c>
       <c r="K20" t="s">
+        <v>258</v>
+      </c>
+      <c r="L20" t="s">
         <v>257</v>
       </c>
-      <c r="L20" t="s">
-        <v>256</v>
-      </c>
       <c r="P20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="W20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21">
         <v>0.98311203837609484</v>
@@ -3012,45 +3041,45 @@
         <v>0.99609999999999999</v>
       </c>
       <c r="H21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J21">
         <v>0.47683269063818606</v>
       </c>
       <c r="K21" t="s">
+        <v>258</v>
+      </c>
+      <c r="L21" t="s">
         <v>257</v>
       </c>
-      <c r="L21" t="s">
-        <v>256</v>
-      </c>
       <c r="P21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R21" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="W21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22">
         <v>0.98311203837609484</v>
@@ -3062,45 +3091,45 @@
         <v>0.96165999999999996</v>
       </c>
       <c r="H22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J22">
         <v>6.6688786721083068E-2</v>
       </c>
       <c r="K22" t="s">
+        <v>258</v>
+      </c>
+      <c r="L22" t="s">
         <v>257</v>
       </c>
-      <c r="L22" t="s">
-        <v>256</v>
-      </c>
       <c r="P22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="W22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23">
         <v>0.49155601918804742</v>
@@ -3112,45 +3141,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J23">
         <v>1.8682785511706303E-2</v>
       </c>
       <c r="K23" t="s">
+        <v>258</v>
+      </c>
+      <c r="L23" t="s">
         <v>257</v>
       </c>
-      <c r="L23" t="s">
-        <v>256</v>
-      </c>
       <c r="P23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V23" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="W23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C24">
         <v>0.98311203837609484</v>
@@ -3162,45 +3191,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J24">
         <v>6.4746879831177079E-2</v>
       </c>
       <c r="K24" t="s">
+        <v>258</v>
+      </c>
+      <c r="L24" t="s">
         <v>257</v>
       </c>
-      <c r="L24" t="s">
-        <v>256</v>
-      </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V24" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W24" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C25">
         <v>0.98311203837609484</v>
@@ -3212,45 +3241,45 @@
         <v>0.96777999999999997</v>
       </c>
       <c r="H25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J25">
         <v>6.120396201617069E-2</v>
       </c>
       <c r="K25" t="s">
+        <v>258</v>
+      </c>
+      <c r="L25" t="s">
         <v>257</v>
       </c>
-      <c r="L25" t="s">
-        <v>256</v>
-      </c>
       <c r="P25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q25" t="s">
+        <v>302</v>
+      </c>
+      <c r="R25" t="s">
         <v>301</v>
       </c>
-      <c r="R25" t="s">
-        <v>300</v>
-      </c>
       <c r="U25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V25" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="W25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26">
         <v>0.49155601918804742</v>
@@ -3262,45 +3291,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J26">
         <v>7.0125316451925546E-2</v>
       </c>
       <c r="K26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L26" t="s">
         <v>257</v>
       </c>
-      <c r="L26" t="s">
-        <v>256</v>
-      </c>
       <c r="P26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V26" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="W26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27">
         <v>1.4746680575641422</v>
@@ -3312,45 +3341,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J27">
         <v>0.12429242027926862</v>
       </c>
       <c r="K27" t="s">
+        <v>258</v>
+      </c>
+      <c r="L27" t="s">
         <v>257</v>
       </c>
-      <c r="L27" t="s">
-        <v>256</v>
-      </c>
       <c r="P27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V27" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="W27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28">
         <v>0.49155601918804742</v>
@@ -3362,45 +3391,45 @@
         <v>0.99351999999999996</v>
       </c>
       <c r="H28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J28">
         <v>4.9074747359742522E-2</v>
       </c>
       <c r="K28" t="s">
+        <v>258</v>
+      </c>
+      <c r="L28" t="s">
         <v>257</v>
       </c>
-      <c r="L28" t="s">
-        <v>256</v>
-      </c>
       <c r="P28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R28" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V28" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W28" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C29">
         <v>0.98311203837609484</v>
@@ -3412,45 +3441,45 @@
         <v>0.99351999999999996</v>
       </c>
       <c r="H29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I29" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J29">
         <v>2.4727445074139667E-2</v>
       </c>
       <c r="K29" t="s">
+        <v>258</v>
+      </c>
+      <c r="L29" t="s">
         <v>257</v>
       </c>
-      <c r="L29" t="s">
-        <v>256</v>
-      </c>
       <c r="P29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="W29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30">
         <v>0.98311203837609484</v>
@@ -3462,45 +3491,45 @@
         <v>0.97119999999999995</v>
       </c>
       <c r="H30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J30">
         <v>2.3624966116599904E-2</v>
       </c>
       <c r="K30" t="s">
+        <v>258</v>
+      </c>
+      <c r="L30" t="s">
         <v>257</v>
       </c>
-      <c r="L30" t="s">
-        <v>256</v>
-      </c>
       <c r="P30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q30" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="W30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C31">
         <v>0.98311203837609484</v>
@@ -3512,45 +3541,45 @@
         <v>0.99772000000000005</v>
       </c>
       <c r="H31" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I31" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J31">
         <v>0.47683269063818606</v>
       </c>
       <c r="K31" t="s">
+        <v>258</v>
+      </c>
+      <c r="L31" t="s">
         <v>257</v>
       </c>
-      <c r="L31" t="s">
-        <v>256</v>
-      </c>
       <c r="P31" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V31" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="W31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32">
         <v>0.49155601918804742</v>
@@ -3562,45 +3591,45 @@
         <v>0.98817999999999995</v>
       </c>
       <c r="H32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J32">
         <v>6.6688786721083068E-2</v>
       </c>
       <c r="K32" t="s">
+        <v>258</v>
+      </c>
+      <c r="L32" t="s">
         <v>257</v>
       </c>
-      <c r="L32" t="s">
-        <v>256</v>
-      </c>
       <c r="P32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="W32" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33">
         <v>0.98311203837609484</v>
@@ -3612,45 +3641,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H33" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J33">
         <v>1.8682785511706303E-2</v>
       </c>
       <c r="K33" t="s">
+        <v>258</v>
+      </c>
+      <c r="L33" t="s">
         <v>257</v>
       </c>
-      <c r="L33" t="s">
-        <v>256</v>
-      </c>
       <c r="P33" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q33" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V33" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="W33" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X33" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C34">
         <v>0.49155601918804742</v>
@@ -3662,45 +3691,45 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="H34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J34">
         <v>6.4746879831177079E-2</v>
       </c>
       <c r="K34" t="s">
+        <v>258</v>
+      </c>
+      <c r="L34" t="s">
         <v>257</v>
       </c>
-      <c r="L34" t="s">
-        <v>256</v>
-      </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V34" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="W34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X34" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C35">
         <v>0.98311203837609484</v>
@@ -3712,45 +3741,45 @@
         <v>0.99927999999999995</v>
       </c>
       <c r="H35" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J35">
         <v>6.120396201617069E-2</v>
       </c>
       <c r="K35" t="s">
+        <v>258</v>
+      </c>
+      <c r="L35" t="s">
         <v>257</v>
       </c>
-      <c r="L35" t="s">
-        <v>256</v>
-      </c>
       <c r="P35" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q35" t="s">
+        <v>302</v>
+      </c>
+      <c r="R35" t="s">
         <v>301</v>
       </c>
-      <c r="R35" t="s">
-        <v>300</v>
-      </c>
       <c r="U35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V35" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="W35" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X35" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C36">
         <v>0.98311203837609484</v>
@@ -3762,45 +3791,45 @@
         <v>0.99939999999999996</v>
       </c>
       <c r="H36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J36">
         <v>7.0125316451925546E-2</v>
       </c>
       <c r="K36" t="s">
+        <v>258</v>
+      </c>
+      <c r="L36" t="s">
         <v>257</v>
       </c>
-      <c r="L36" t="s">
-        <v>256</v>
-      </c>
       <c r="P36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q36" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V36" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="W36" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X36" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C37">
         <v>0.98311203837609484</v>
@@ -3812,45 +3841,45 @@
         <v>0.99892000000000003</v>
       </c>
       <c r="H37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J37">
         <v>0.12429242027926862</v>
       </c>
       <c r="K37" t="s">
+        <v>258</v>
+      </c>
+      <c r="L37" t="s">
         <v>257</v>
       </c>
-      <c r="L37" t="s">
-        <v>256</v>
-      </c>
       <c r="P37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q37" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="W37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X37" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C38">
         <v>0.49155601918804742</v>
@@ -3862,45 +3891,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I38" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J38">
         <v>4.9074747359742522E-2</v>
       </c>
       <c r="K38" t="s">
+        <v>258</v>
+      </c>
+      <c r="L38" t="s">
         <v>257</v>
       </c>
-      <c r="L38" t="s">
-        <v>256</v>
-      </c>
       <c r="P38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q38" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W38" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C39">
         <v>0.98311203837609484</v>
@@ -3912,45 +3941,45 @@
         <v>0.98775999999999997</v>
       </c>
       <c r="H39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J39">
         <v>2.4727445074139667E-2</v>
       </c>
       <c r="K39" t="s">
+        <v>258</v>
+      </c>
+      <c r="L39" t="s">
         <v>257</v>
       </c>
-      <c r="L39" t="s">
-        <v>256</v>
-      </c>
       <c r="P39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q39" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V39" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W39" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X39" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40">
         <v>0.98311203837609484</v>
@@ -3962,45 +3991,45 @@
         <v>0.99465999999999999</v>
       </c>
       <c r="H40" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J40">
         <v>2.3624966116599904E-2</v>
       </c>
       <c r="K40" t="s">
+        <v>258</v>
+      </c>
+      <c r="L40" t="s">
         <v>257</v>
       </c>
-      <c r="L40" t="s">
-        <v>256</v>
-      </c>
       <c r="P40" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V40" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W40" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C41">
         <v>0.98311203837609484</v>
@@ -4012,45 +4041,45 @@
         <v>0.97984000000000004</v>
       </c>
       <c r="H41" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J41">
         <v>0.47683269063818606</v>
       </c>
       <c r="K41" t="s">
+        <v>258</v>
+      </c>
+      <c r="L41" t="s">
         <v>257</v>
       </c>
-      <c r="L41" t="s">
-        <v>256</v>
-      </c>
       <c r="P41" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="W41" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X41" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C42">
         <v>0.98311203837609484</v>
@@ -4062,45 +4091,45 @@
         <v>0.95733999999999997</v>
       </c>
       <c r="H42" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J42">
         <v>6.6688786721083068E-2</v>
       </c>
       <c r="K42" t="s">
+        <v>258</v>
+      </c>
+      <c r="L42" t="s">
         <v>257</v>
       </c>
-      <c r="L42" t="s">
-        <v>256</v>
-      </c>
       <c r="P42" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q42" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V42" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="W42" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X42" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C43">
         <v>0.98311203837609484</v>
@@ -4112,45 +4141,45 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="H43" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J43">
         <v>1.8682785511706303E-2</v>
       </c>
       <c r="K43" t="s">
+        <v>258</v>
+      </c>
+      <c r="L43" t="s">
         <v>257</v>
       </c>
-      <c r="L43" t="s">
-        <v>256</v>
-      </c>
       <c r="P43" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R43" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V43" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="W43" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X43" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C44">
         <v>0.98311203837609484</v>
@@ -4162,21 +4191,21 @@
         <v>0.997</v>
       </c>
       <c r="U44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V44" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="W44" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X44" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C45">
         <v>0.49155601918804742</v>
@@ -4188,21 +4217,21 @@
         <v>0.99994000000000005</v>
       </c>
       <c r="U45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V45" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="W45" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X45" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C46">
         <v>0.49155601918804742</v>
@@ -4214,21 +4243,21 @@
         <v>0.99994000000000005</v>
       </c>
       <c r="U46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V46" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="W46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="X46" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C47">
         <v>0.49155601918804742</v>
@@ -4240,21 +4269,21 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="U47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V47" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="W47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="X47" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C48">
         <v>0.98311203837609484</v>
@@ -4266,21 +4295,21 @@
         <v>0.99453999999999998</v>
       </c>
       <c r="U48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V48" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="W48" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="X48" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C49">
         <v>0.98311203837609484</v>
@@ -4292,21 +4321,21 @@
         <v>0.99436000000000002</v>
       </c>
       <c r="U49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="W49" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C50">
         <v>0.98311203837609484</v>
@@ -4318,21 +4347,21 @@
         <v>0.99946000000000002</v>
       </c>
       <c r="U50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V50" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="W50" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C51">
         <v>0.98311203837609484</v>
@@ -4344,21 +4373,21 @@
         <v>0.95872000000000002</v>
       </c>
       <c r="U51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V51" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="W51" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C52">
         <v>0.49155601918804742</v>
@@ -4370,21 +4399,21 @@
         <v>0.98284000000000005</v>
       </c>
       <c r="U52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V52" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="W52" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53">
         <v>0.98311203837609484</v>
@@ -4396,21 +4425,21 @@
         <v>0.99334</v>
       </c>
       <c r="U53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V53" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="W53" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C54">
         <v>0.98311203837609484</v>
@@ -4422,21 +4451,21 @@
         <v>0.98277999999999999</v>
       </c>
       <c r="U54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V54" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="W54" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C55">
         <v>0.98311203837609484</v>
@@ -4448,21 +4477,21 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="U55" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V55" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="W55" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X55" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C56">
         <v>0.49155601918804742</v>
@@ -4474,21 +4503,21 @@
         <v>0.98961999999999994</v>
       </c>
       <c r="U56" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V56" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="W56" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X56" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C57">
         <v>0.98311203837609484</v>
@@ -4500,21 +4529,21 @@
         <v>0.99748000000000003</v>
       </c>
       <c r="U57" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V57" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="W57" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X57" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C58">
         <v>0.98311203837609484</v>
@@ -4526,21 +4555,21 @@
         <v>0.99219999999999997</v>
       </c>
       <c r="U58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V58" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="W58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="X58" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C59">
         <v>0.49155601918804742</v>
@@ -4552,21 +4581,21 @@
         <v>0.99904000000000004</v>
       </c>
       <c r="U59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V59" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="W59" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="X59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C60">
         <v>0.98311203837609484</v>
@@ -4578,21 +4607,21 @@
         <v>0.99819999999999998</v>
       </c>
       <c r="U60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V60" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="W60" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="X60" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C61">
         <v>0.49155601918804742</v>
@@ -4604,21 +4633,21 @@
         <v>0.99873999999999996</v>
       </c>
       <c r="U61" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X61" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C62">
         <v>0.98311203837609484</v>
@@ -4630,21 +4659,21 @@
         <v>0.99778</v>
       </c>
       <c r="U62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V62" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W62" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X62" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C63">
         <v>0.49155601918804742</v>
@@ -4656,21 +4685,21 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="U63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V63" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="W63" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X63" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C64">
         <v>0.98311203837609484</v>
@@ -4682,21 +4711,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V64" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="W64" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X64" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C65">
         <v>0.98311203837609484</v>
@@ -4708,21 +4737,21 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="U65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V65" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="W65" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X65" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C66">
         <v>0.49155601918804742</v>
@@ -4734,21 +4763,21 @@
         <v>0.9778</v>
       </c>
       <c r="U66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V66" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="W66" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X66" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C67">
         <v>0.49155601918804742</v>
@@ -4760,21 +4789,21 @@
         <v>0.99856</v>
       </c>
       <c r="U67" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V67" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="W67" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X67" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C68">
         <v>0.98311203837609484</v>
@@ -4786,21 +4815,21 @@
         <v>0.99724000000000002</v>
       </c>
       <c r="U68" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V68" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="W68" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X68" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C69">
         <v>0.49155601918804742</v>
@@ -4812,21 +4841,21 @@
         <v>0.95565999999999995</v>
       </c>
       <c r="U69" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V69" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="W69" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C70">
         <v>0.49155601918804742</v>
@@ -4838,21 +4867,21 @@
         <v>0.95554000000000006</v>
       </c>
       <c r="U70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V70" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W70" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X70" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C71">
         <v>0.49155601918804742</v>
@@ -4864,21 +4893,21 @@
         <v>0.97138000000000002</v>
       </c>
       <c r="U71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V71" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W71" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X71" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C72">
         <v>0.98311203837609484</v>
@@ -4890,21 +4919,21 @@
         <v>0.99070000000000003</v>
       </c>
       <c r="U72" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V72" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W72" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C73">
         <v>0.98311203837609484</v>
@@ -4916,21 +4945,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V73" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="W73" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X73" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74">
         <v>0.98311203837609484</v>
@@ -4942,21 +4971,21 @@
         <v>0.99880000000000002</v>
       </c>
       <c r="U74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V74" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="W74" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C75">
         <v>0.98311203837609484</v>
@@ -4968,21 +4997,21 @@
         <v>0.95728000000000002</v>
       </c>
       <c r="U75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="W75" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X75" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C76">
         <v>0.98311203837609484</v>
@@ -4994,21 +5023,21 @@
         <v>0.97516000000000003</v>
       </c>
       <c r="U76" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V76" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="W76" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X76" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C77">
         <v>0.49155601918804742</v>
@@ -5020,21 +5049,21 @@
         <v>0.99790000000000001</v>
       </c>
       <c r="U77" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V77" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="W77" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X77" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C78">
         <v>0.49155601918804742</v>
@@ -5046,21 +5075,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V78" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="W78" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C79">
         <v>0.49155601918804742</v>
@@ -5072,21 +5101,21 @@
         <v>0.99873999999999996</v>
       </c>
       <c r="U79" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V79" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W79" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C80">
         <v>0.98311203837609484</v>
@@ -5098,21 +5127,21 @@
         <v>0.97611999999999999</v>
       </c>
       <c r="U80" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V80" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W80" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X80" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C81">
         <v>0.98311203837609484</v>
@@ -5124,21 +5153,21 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="U81" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W81" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C82">
         <v>0.98311203837609484</v>
@@ -5150,21 +5179,21 @@
         <v>0.94443999999999995</v>
       </c>
       <c r="U82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V82" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="W82" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="X82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C83">
         <v>0.98311203837609484</v>
@@ -5176,21 +5205,21 @@
         <v>0.98877999999999999</v>
       </c>
       <c r="U83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V83" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="W83" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="X83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="84" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C84">
         <v>0.98311203837609484</v>
@@ -5202,21 +5231,21 @@
         <v>0.96550000000000002</v>
       </c>
       <c r="U84" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V84" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="W84" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="X84" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C85">
         <v>0.98311203837609484</v>
@@ -5228,21 +5257,21 @@
         <v>0.94947999999999999</v>
       </c>
       <c r="U85" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V85" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="W85" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X85" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C86">
         <v>0.98311203837609484</v>
@@ -5254,21 +5283,21 @@
         <v>0.99807999999999997</v>
       </c>
       <c r="U86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V86" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="W86" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X86" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C87">
         <v>0.98311203837609484</v>
@@ -5280,21 +5309,21 @@
         <v>0.99172000000000005</v>
       </c>
       <c r="U87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V87" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="W87" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X87" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C88">
         <v>0.98311203837609484</v>
@@ -5306,21 +5335,21 @@
         <v>0.99958000000000002</v>
       </c>
       <c r="U88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V88" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="W88" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X88" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C89">
         <v>0.98311203837609484</v>
@@ -5332,21 +5361,21 @@
         <v>0.99453999999999998</v>
       </c>
       <c r="U89" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V89" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="W89" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X89" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C90">
         <v>0.98311203837609484</v>
@@ -5358,21 +5387,21 @@
         <v>0.99873999999999996</v>
       </c>
       <c r="U90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V90" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="W90" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X90" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C91">
         <v>0.98311203837609484</v>
@@ -5384,21 +5413,21 @@
         <v>0.97984000000000004</v>
       </c>
       <c r="U91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V91" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="W91" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X91" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C92">
         <v>0.98311203837609484</v>
@@ -5410,21 +5439,21 @@
         <v>0.98260000000000003</v>
       </c>
       <c r="U92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V92" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="W92" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X92" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C93">
         <v>0.98311203837609484</v>
@@ -5436,21 +5465,21 @@
         <v>0.98806000000000005</v>
       </c>
       <c r="U93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V93" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="W93" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X93" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="94" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C94">
         <v>0.98311203837609484</v>
@@ -5462,21 +5491,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U94" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V94" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="W94" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X94" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C95">
         <v>0.98311203837609484</v>
@@ -5488,21 +5517,21 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="U95" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V95" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="W95" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X95" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C96">
         <v>0.98311203837609484</v>
@@ -5514,21 +5543,21 @@
         <v>0.97719999999999996</v>
       </c>
       <c r="U96" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V96" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="W96" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X96" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="97" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C97">
         <v>0.98311203837609484</v>
@@ -5540,21 +5569,21 @@
         <v>0.99909999999999999</v>
       </c>
       <c r="U97" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V97" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W97" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X97" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C98">
         <v>0.49155601918804742</v>
@@ -5566,21 +5595,21 @@
         <v>0.99802000000000002</v>
       </c>
       <c r="U98" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V98" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W98" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C99">
         <v>0.98311203837609484</v>
@@ -5592,21 +5621,21 @@
         <v>0.99453999999999998</v>
       </c>
       <c r="U99" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V99" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="W99" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C100">
         <v>0.98311203837609484</v>
@@ -5618,21 +5647,21 @@
         <v>0.99675999999999998</v>
       </c>
       <c r="U100" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V100" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="W100" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X100" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C101">
         <v>0.49155601918804742</v>
@@ -5644,21 +5673,21 @@
         <v>0.97065999999999997</v>
       </c>
       <c r="U101" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V101" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="W101" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X101" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="102" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C102">
         <v>0.49155601918804742</v>
@@ -5670,21 +5699,21 @@
         <v>0.99495999999999996</v>
       </c>
       <c r="U102" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V102" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="W102" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X102" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C103">
         <v>0.98311203837609484</v>
@@ -5696,21 +5725,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U103" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V103" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="W103" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X103" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="104" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C104">
         <v>0.98311203837609484</v>
@@ -5722,21 +5751,21 @@
         <v>0.99495999999999996</v>
       </c>
       <c r="U104" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V104" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="W104" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X104" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C105">
         <v>0.98311203837609484</v>
@@ -5748,21 +5777,21 @@
         <v>0.99838000000000005</v>
       </c>
       <c r="U105" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V105" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="W105" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X105" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="106" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C106">
         <v>0.49155601918804742</v>
@@ -5774,21 +5803,21 @@
         <v>0.92212000000000005</v>
       </c>
       <c r="U106" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V106" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="W106" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X106" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C107">
         <v>0.98311203837609484</v>
@@ -5800,21 +5829,21 @@
         <v>0.97485999999999995</v>
       </c>
       <c r="U107" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V107" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="W107" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X107" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="108" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C108">
         <v>0.49155601918804742</v>
@@ -5826,21 +5855,21 @@
         <v>0.91905999999999999</v>
       </c>
       <c r="U108" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V108" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="W108" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X108" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="109" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C109">
         <v>0.98311203837609484</v>
@@ -5852,21 +5881,21 @@
         <v>0.99922</v>
       </c>
       <c r="U109" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V109" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="W109" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X109" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="110" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C110">
         <v>0.98311203837609484</v>
@@ -5878,21 +5907,21 @@
         <v>0.99814000000000003</v>
       </c>
       <c r="U110" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V110" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="W110" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X110" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="111" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C111">
         <v>0.49155601918804742</v>
@@ -5904,21 +5933,21 @@
         <v>0.99778</v>
       </c>
       <c r="U111" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V111" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="W111" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X111" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="112" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C112">
         <v>0.98311203837609484</v>
@@ -5930,21 +5959,21 @@
         <v>0.99778</v>
       </c>
       <c r="U112" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V112" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="W112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X112" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="113" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C113">
         <v>0.98311203837609484</v>
@@ -5956,21 +5985,21 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="U113" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V113" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W113" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X113" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="114" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C114">
         <v>0.98311203837609484</v>
@@ -5982,21 +6011,21 @@
         <v>0.99129999999999996</v>
       </c>
       <c r="U114" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V114" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="W114" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X114" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="115" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C115">
         <v>1.9662240767521897</v>
@@ -6008,21 +6037,21 @@
         <v>0.99970000000000003</v>
       </c>
       <c r="U115" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V115" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="W115" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="X115" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="116" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C116">
         <v>0.49155601918804742</v>
@@ -6034,21 +6063,21 @@
         <v>0.98409999999999997</v>
       </c>
       <c r="U116" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V116" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="W116" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X116" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="117" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C117">
         <v>0.98311203837609484</v>
@@ -6060,21 +6089,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U117" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V117" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="W117" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="X117" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="118" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C118">
         <v>0.98311203837609484</v>
@@ -6086,21 +6115,21 @@
         <v>0.99531999999999998</v>
       </c>
       <c r="U118" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V118" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="W118" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="X118" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="119" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C119">
         <v>0.98311203837609484</v>
@@ -6112,21 +6141,21 @@
         <v>0.98218000000000005</v>
       </c>
       <c r="U119" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V119" t="s">
+        <v>408</v>
+      </c>
+      <c r="W119" t="s">
         <v>407</v>
       </c>
-      <c r="W119" t="s">
-        <v>406</v>
-      </c>
       <c r="X119" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="120" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C120">
         <v>0.98311203837609484</v>
@@ -6138,21 +6167,21 @@
         <v>0.99970000000000003</v>
       </c>
       <c r="U120" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V120" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="W120" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="X120" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="121" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C121">
         <v>0.98311203837609484</v>
@@ -6164,21 +6193,21 @@
         <v>0.99370000000000003</v>
       </c>
       <c r="U121" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V121" t="s">
+        <v>411</v>
+      </c>
+      <c r="W121" t="s">
         <v>410</v>
       </c>
-      <c r="W121" t="s">
-        <v>409</v>
-      </c>
       <c r="X121" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="122" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C122">
         <v>0.98311203837609484</v>
@@ -6190,21 +6219,21 @@
         <v>0.99904000000000004</v>
       </c>
       <c r="U122" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V122" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="W122" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="X122" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="123" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C123">
         <v>0.98311203837609484</v>
@@ -6216,21 +6245,21 @@
         <v>0.99958000000000002</v>
       </c>
       <c r="U123" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V123" t="s">
+        <v>414</v>
+      </c>
+      <c r="W123" t="s">
         <v>413</v>
       </c>
-      <c r="W123" t="s">
-        <v>412</v>
-      </c>
       <c r="X123" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="124" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C124">
         <v>0.98311203837609484</v>
@@ -6242,21 +6271,21 @@
         <v>0.99909999999999999</v>
       </c>
       <c r="U124" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V124" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="W124" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="X124" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="125" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C125">
         <v>0.98311203837609484</v>
@@ -6268,21 +6297,21 @@
         <v>0.99261999999999995</v>
       </c>
       <c r="U125" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V125" t="s">
+        <v>417</v>
+      </c>
+      <c r="W125" t="s">
         <v>416</v>
       </c>
-      <c r="W125" t="s">
-        <v>415</v>
-      </c>
       <c r="X125" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="126" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C126">
         <v>0.98311203837609484</v>
@@ -6294,21 +6323,21 @@
         <v>0.99309999999999998</v>
       </c>
       <c r="U126" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V126" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="W126" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="X126" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="127" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C127">
         <v>1.9662240767521897</v>
@@ -6320,21 +6349,21 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="U127" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V127" t="s">
+        <v>420</v>
+      </c>
+      <c r="W127" t="s">
         <v>419</v>
       </c>
-      <c r="W127" t="s">
-        <v>418</v>
-      </c>
       <c r="X127" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="128" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C128">
         <v>0.49155601918804742</v>
@@ -6346,21 +6375,21 @@
         <v>0.98482000000000003</v>
       </c>
       <c r="U128" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V128" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="W128" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="X128" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="129" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C129">
         <v>0.49155601918804742</v>
@@ -6372,21 +6401,21 @@
         <v>0.98499999999999999</v>
       </c>
       <c r="U129" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V129" t="s">
+        <v>423</v>
+      </c>
+      <c r="W129" t="s">
         <v>422</v>
       </c>
-      <c r="W129" t="s">
-        <v>421</v>
-      </c>
       <c r="X129" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="130" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C130">
         <v>0.49155601918804742</v>
@@ -6398,21 +6427,21 @@
         <v>0.99214000000000002</v>
       </c>
       <c r="U130" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V130" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="W130" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="X130" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="131" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C131">
         <v>0.49155601918804742</v>
@@ -6424,21 +6453,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U131" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V131" t="s">
+        <v>426</v>
+      </c>
+      <c r="W131" t="s">
         <v>425</v>
       </c>
-      <c r="W131" t="s">
-        <v>424</v>
-      </c>
       <c r="X131" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="132" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C132">
         <v>0.98311203837609484</v>
@@ -6450,21 +6479,21 @@
         <v>0.99909999999999999</v>
       </c>
       <c r="U132" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V132" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="W132" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="X132" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C133">
         <v>0.98311203837609484</v>
@@ -6476,21 +6505,21 @@
         <v>0.99909999999999999</v>
       </c>
       <c r="U133" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V133" t="s">
+        <v>429</v>
+      </c>
+      <c r="W133" t="s">
         <v>428</v>
       </c>
-      <c r="W133" t="s">
-        <v>427</v>
-      </c>
       <c r="X133" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="134" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C134">
         <v>1.9662240767521897</v>
@@ -6502,21 +6531,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U134" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V134" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="W134" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="X134" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="135" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C135">
         <v>0.49155601918804742</v>
@@ -6528,21 +6557,21 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="U135" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V135" t="s">
+        <v>432</v>
+      </c>
+      <c r="W135" t="s">
         <v>431</v>
       </c>
-      <c r="W135" t="s">
-        <v>430</v>
-      </c>
       <c r="X135" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="136" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C136">
         <v>1.9662240767521897</v>
@@ -6554,21 +6583,21 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="U136" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V136" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="W136" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="X136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="137" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C137">
         <v>1.9662240767521897</v>
@@ -6580,21 +6609,21 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U137" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V137" t="s">
+        <v>435</v>
+      </c>
+      <c r="W137" t="s">
         <v>434</v>
       </c>
-      <c r="W137" t="s">
-        <v>433</v>
-      </c>
       <c r="X137" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="138" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C138">
         <v>0.98311203837609484</v>
@@ -6606,21 +6635,21 @@
         <v>0.99843999999999999</v>
       </c>
       <c r="U138" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V138" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="W138" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X138" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="139" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C139">
         <v>0.98311203837609484</v>
@@ -6632,21 +6661,21 @@
         <v>0.99814000000000003</v>
       </c>
       <c r="U139" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V139" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="W139" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="X139" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="140" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C140">
         <v>0.49155601918804742</v>
@@ -6658,21 +6687,21 @@
         <v>0.99958000000000002</v>
       </c>
       <c r="U140" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V140" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="W140" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="X140" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="141" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C141">
         <v>0.98311203837609484</v>
@@ -6684,21 +6713,21 @@
         <v>0.99160000000000004</v>
       </c>
       <c r="U141" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V141" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="W141" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="X141" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="142" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C142">
         <v>0.98311203837609484</v>
@@ -6710,21 +6739,21 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="U142" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V142" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="W142" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X142" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="143" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C143">
         <v>0.98311203837609484</v>
@@ -6736,21 +6765,21 @@
         <v>0.99909999999999999</v>
       </c>
       <c r="U143" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V143" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="W143" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X143" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="144" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B144" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C144">
         <v>0.98311203837609484</v>
@@ -6762,21 +6791,21 @@
         <v>0.99922</v>
       </c>
       <c r="U144" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V144" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="W144" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="145" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B145" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C145">
         <v>0.98311203837609484</v>
@@ -6788,21 +6817,21 @@
         <v>0.99382000000000004</v>
       </c>
       <c r="U145" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V145" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="W145" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X145" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="146" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C146">
         <v>0.49155601918804742</v>
@@ -6814,21 +6843,21 @@
         <v>0.99873999999999996</v>
       </c>
       <c r="U146" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V146" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="W146" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="147" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C147">
         <v>0.98311203837609484</v>
@@ -6840,21 +6869,21 @@
         <v>0.98692000000000002</v>
       </c>
       <c r="U147" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V147" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="W147" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="X147" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="148" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C148">
         <v>0.49155601918804742</v>
@@ -6866,21 +6895,21 @@
         <v>0.99838000000000005</v>
       </c>
       <c r="U148" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V148" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="W148" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="X148" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="149" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B149" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C149">
         <v>0.98311203837609484</v>
@@ -6892,21 +6921,21 @@
         <v>0.99160000000000004</v>
       </c>
       <c r="U149" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V149" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="W149" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="X149" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="150" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C150">
         <v>0.98311203837609484</v>
@@ -6918,21 +6947,21 @@
         <v>0.98968</v>
       </c>
       <c r="U150" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V150" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="W150" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X150" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="151" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C151">
         <v>0.98311203837609484</v>
@@ -6944,21 +6973,21 @@
         <v>0.99795999999999996</v>
       </c>
       <c r="U151" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V151" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="W151" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="X151" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="152" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C152">
         <v>0.49155601918804742</v>
@@ -6970,21 +6999,21 @@
         <v>0.99502000000000002</v>
       </c>
       <c r="U152" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V152" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="W152" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X152" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="153" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B153" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C153">
         <v>0.49155601918804742</v>
@@ -6996,21 +7025,21 @@
         <v>0.90849999999999997</v>
       </c>
       <c r="U153" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V153" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="W153" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X153" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="154" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B154" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C154">
         <v>0.98311203837609484</v>
@@ -7022,21 +7051,21 @@
         <v>0.98440000000000005</v>
       </c>
       <c r="U154" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V154" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="W154" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X154" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="155" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C155">
         <v>0.98311203837609484</v>
@@ -7048,21 +7077,21 @@
         <v>0.97821999999999998</v>
       </c>
       <c r="U155" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V155" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="W155" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="X155" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="156" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C156">
         <v>0.98311203837609484</v>
@@ -7074,21 +7103,21 @@
         <v>0.95787999999999995</v>
       </c>
       <c r="U156" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V156" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="W156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X156" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="157" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B157" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C157">
         <v>0.98311203837609484</v>
@@ -7100,21 +7129,21 @@
         <v>0.98380000000000001</v>
       </c>
       <c r="U157" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V157" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="W157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="X157" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="158" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B158" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C158">
         <v>0.98311203837609484</v>
@@ -7126,21 +7155,21 @@
         <v>0.98799999999999999</v>
       </c>
       <c r="U158" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V158" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="W158" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X158" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="159" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C159">
         <v>0.98311203837609484</v>
@@ -7152,352 +7181,352 @@
         <v>0.99346000000000001</v>
       </c>
       <c r="U159" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V159" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="W159" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="X159" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="160" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U160" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V160" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="W160" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X160" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="161" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U161" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V161" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="W161" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="X161" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="162" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U162" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V162" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="W162" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X162" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="163" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U163" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V163" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="W163" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="X163" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="164" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U164" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V164" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="W164" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="X164" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="165" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U165" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V165" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="W165" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="X165" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="166" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U166" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V166" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="W166" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X166" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="167" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U167" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V167" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="W167" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="X167" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="168" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U168" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V168" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="W168" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X168" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="169" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U169" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V169" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="W169" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="X169" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="170" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U170" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V170" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="W170" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X170" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="171" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U171" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V171" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="W171" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X171" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="172" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U172" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V172" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="W172" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X172" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="173" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U173" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V173" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="W173" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X173" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="174" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U174" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V174" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="W174" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X174" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="175" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U175" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V175" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="W175" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X175" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="176" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U176" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V176" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="W176" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X176" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="177" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U177" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V177" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="W177" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="X177" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="178" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U178" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V178" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="W178" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X178" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="179" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U179" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V179" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="W179" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X179" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="180" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U180" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V180" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="W180" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X180" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="181" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U181" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V181" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="W181" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="X181" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="182" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U182" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V182" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="W182" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X182" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="183" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U183" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V183" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="W183" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X183" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -7620,15 +7649,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.57943469536758585</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -7660,7 +7686,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -7909,7 +7935,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3">
         <v>0.24174053182916999</v>
@@ -8259,12 +8285,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -8293,7 +8319,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <v>1.5</v>
@@ -8614,7 +8640,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -8740,7 +8766,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -8866,7 +8892,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -8992,7 +9018,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -9118,7 +9144,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -9244,7 +9270,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -9370,7 +9396,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -9496,7 +9522,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -9622,7 +9648,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -9748,7 +9774,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -9874,7 +9900,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -10000,7 +10026,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -10126,7 +10152,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -10252,7 +10278,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -10378,7 +10404,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -10504,7 +10530,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -10630,7 +10656,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -10756,7 +10782,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -10882,7 +10908,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -11008,7 +11034,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -11134,7 +11160,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -11260,7 +11286,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -11386,7 +11412,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -11512,7 +11538,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -11632,7 +11658,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -11752,7 +11778,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -11872,7 +11898,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -11992,7 +12018,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -12112,7 +12138,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -12232,7 +12258,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -12352,7 +12378,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -12472,7 +12498,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -12592,7 +12618,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -12712,7 +12738,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -12832,7 +12858,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -12952,7 +12978,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -13072,7 +13098,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -13192,7 +13218,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -13312,7 +13338,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -13432,7 +13458,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -13552,7 +13578,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -13672,7 +13698,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -13792,7 +13818,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -13912,7 +13938,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -14032,7 +14058,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -14152,7 +14178,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -14272,7 +14298,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -14392,7 +14418,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -14518,7 +14544,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -14644,7 +14670,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -14770,7 +14796,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -14896,7 +14922,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -15022,7 +15048,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -15148,7 +15174,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -15274,7 +15300,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -15400,7 +15426,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -15526,7 +15552,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -15652,7 +15678,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -15778,7 +15804,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -15904,7 +15930,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -16030,7 +16056,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -16156,7 +16182,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -16282,7 +16308,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -16408,7 +16434,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -16534,7 +16560,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -16660,7 +16686,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -16786,7 +16812,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -16912,7 +16938,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -17038,7 +17064,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -17164,7 +17190,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -17290,7 +17316,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -17416,7 +17442,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5984F0A2-A93D-4A64-AE9B-30F7E5B6E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0646D19B-1044-41AE-8A72-18F106835850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -2076,7 +2076,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D611C2-F6F4-45B3-B13B-165722A91E97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8306F29A-E865-4D13-83A9-043C7A6EAAC6}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0646D19B-1044-41AE-8A72-18F106835850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2214D12F-A6DF-4352-BAF9-AB19EF65C154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -2076,7 +2076,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8306F29A-E865-4D13-83A9-043C7A6EAAC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E678CC-CACF-48AA-BFFA-731AE1AAF535}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2214D12F-A6DF-4352-BAF9-AB19EF65C154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AF0C9B3-8193-49B2-A5AF-EFB5E49C1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2076,7 +2076,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E678CC-CACF-48AA-BFFA-731AE1AAF535}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4281BF4-9AF9-4352-9ACA-F3576FC7FA1F}">
   <dimension ref="B2:AE183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AF0C9B3-8193-49B2-A5AF-EFB5E49C1EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C8D183F-56A1-4511-811C-249FDB407B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="577">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1188,144 +1188,321 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_r17609399-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ12-220</t>
+    <t>Bioenergy + CCUS_w94053861-220</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w94053861-220</t>
+  </si>
+  <si>
+    <t>CCGT_w94053861-220</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w94053861-220</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w94053861-220</t>
+  </si>
+  <si>
+    <t>Gas turbine_w94053861-220</t>
+  </si>
+  <si>
+    <t>IGCC_w94053861-220</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w94053861-220</t>
+  </si>
+  <si>
+    <t>Nuclear large_w94053861-220</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w94053861-220</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w94053861-220</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w94053861-220</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w94053861-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ12-220</t>
   </si>
   <si>
     <t>e_NZ12-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w270018358-220</t>
+    <t>EN_Hydro_NZL-2_NZ12-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ12-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w270018358-220</t>
   </si>
   <si>
     <t>e_w270018358-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w93556808-220</t>
+    <t>EN_Hydro_NZL-2_w270018358-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w270018358-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w93556808-220</t>
   </si>
   <si>
     <t>e_w93556808-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w89637174-220</t>
+    <t>EN_Hydro_NZL-2_w93556808-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w93556808-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w89637174-220</t>
   </si>
   <si>
     <t>e_w89637174-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w89664063-220</t>
+    <t>EN_Hydro_NZL-2_w89637174-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w89637174-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w89664063-220</t>
   </si>
   <si>
     <t>e_w89664063-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ40-220</t>
+    <t>EN_Hydro_NZL-2_w89664063-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w89664063-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ40-220</t>
   </si>
   <si>
     <t>e_NZ40-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ11-220</t>
+    <t>EN_Hydro_NZL-2_NZ40-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ40-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ11-220</t>
   </si>
   <si>
     <t>e_NZ11-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w412589726-220</t>
+    <t>EN_Hydro_NZL-2_NZ11-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ11-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w180514007-220</t>
+  </si>
+  <si>
+    <t>e_w180514007-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-2_w180514007-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w180514007-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w412589726-220</t>
   </si>
   <si>
     <t>e_w412589726-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w87928925-220</t>
+    <t>EN_Hydro_NZL-2_w412589726-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w412589726-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w87928925-220</t>
   </si>
   <si>
     <t>e_w87928925-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ13-220</t>
+    <t>EN_Hydro_NZL-2_w87928925-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w87928925-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ13-220</t>
   </si>
   <si>
     <t>e_NZ13-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w272522517-220</t>
+    <t>EN_Hydro_NZL-2_NZ13-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ13-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w272522517-220</t>
   </si>
   <si>
     <t>e_w272522517-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ33-220</t>
+    <t>EN_Hydro_NZL-2_w272522517-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w272522517-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ33-220</t>
   </si>
   <si>
     <t>e_NZ33-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ35-220</t>
+    <t>EN_Hydro_NZL-2_NZ33-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ33-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ35-220</t>
   </si>
   <si>
     <t>e_NZ35-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w89636266-220</t>
+    <t>EN_Hydro_NZL-2_NZ35-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ35-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w89636266-220</t>
   </si>
   <si>
     <t>e_w89636266-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ22-220</t>
+    <t>EN_Hydro_NZL-2_w89636266-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w89636266-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ22-220</t>
   </si>
   <si>
     <t>e_NZ22-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w180514007-220</t>
-  </si>
-  <si>
-    <t>e_w180514007-220</t>
-  </si>
-  <si>
-    <t>EN_Hydro_NZ30-220</t>
+    <t>EN_Hydro_NZL-2_NZ22-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ22-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ30-220</t>
   </si>
   <si>
     <t>e_NZ30-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w89411122-220</t>
+    <t>EN_Hydro_NZL-2_NZ30-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ30-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w89411122-220</t>
   </si>
   <si>
     <t>e_w89411122-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w95512216-220</t>
+    <t>EN_Hydro_NZL-2_w89411122-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w89411122-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w95512216-220</t>
   </si>
   <si>
     <t>e_w95512216-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w169512273-220</t>
+    <t>EN_Hydro_NZL-2_w95512216-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w95512216-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w169512273-220</t>
   </si>
   <si>
     <t>e_w169512273-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w270521928-220</t>
+    <t>EN_Hydro_NZL-2_w169512273-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w169512273-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w270521928-220</t>
   </si>
   <si>
     <t>e_w270521928-220</t>
   </si>
   <si>
-    <t>EN_Hydro_w89637173-220</t>
+    <t>EN_Hydro_NZL-2_w270521928-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w270521928-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_w89637173-220</t>
   </si>
   <si>
     <t>e_w89637173-220</t>
   </si>
   <si>
-    <t>EN_Hydro_NZ14-220</t>
+    <t>EN_Hydro_NZL-2_w89637173-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_w89637173-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-1_NZ14-220</t>
   </si>
   <si>
     <t>e_NZ14-220</t>
   </si>
   <si>
+    <t>EN_Hydro_NZL-2_NZ14-220</t>
+  </si>
+  <si>
+    <t>EN_Hydro_NZL-3_NZ14-220</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_w188180344-220</t>
   </si>
   <si>
@@ -1344,6 +1521,81 @@
     <t>EN_STG4hbNREL_r17609399-220</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w94053861-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w94053861-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w1026587442-220</t>
+  </si>
+  <si>
+    <t>e_w1026587442-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w1026587442-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w167572576-220</t>
+  </si>
+  <si>
+    <t>e_w167572576-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w167572576-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_NZ42-220</t>
+  </si>
+  <si>
+    <t>e_NZ42-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_NZ42-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_NZ23-220</t>
+  </si>
+  <si>
+    <t>e_NZ23-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_NZ23-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w89636266-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w89636266-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w414953388-220</t>
+  </si>
+  <si>
+    <t>e_w414953388-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w414953388-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w89636510-220</t>
+  </si>
+  <si>
+    <t>e_w89636510-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w89636510-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_NZ31-220</t>
+  </si>
+  <si>
+    <t>e_NZ31-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_NZ31-220</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_w148300699-220</t>
   </si>
   <si>
@@ -1407,6 +1659,15 @@
     <t>EN_STG4hbNREL_NZ16-220</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w270022030-220</t>
+  </si>
+  <si>
+    <t>e_w270022030-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w270022030-220</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_NZ17-220</t>
   </si>
   <si>
@@ -1476,6 +1737,12 @@
     <t>EN_STG4hbNREL_NZ11-220</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w180514007-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w180514007-220</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_w412589726-220</t>
   </si>
   <si>
@@ -1512,24 +1779,12 @@
     <t>EN_STG4hbNREL_NZ35-220</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_w89636266-220</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89636266-220</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_NZ22-220</t>
   </si>
   <si>
     <t>EN_STG4hbNREL_NZ22-220</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL_w180514007-220</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w180514007-220</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL_NZ30-220</t>
   </si>
   <si>
@@ -1570,6 +1825,15 @@
   </si>
   <si>
     <t>EN_STG4hbNREL_NZ14-220</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_w94840399-220</t>
+  </si>
+  <si>
+    <t>e_w94840399-220</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w94840399-220</t>
   </si>
   <si>
     <t>ELC</t>
@@ -2076,8 +2340,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4281BF4-9AF9-4352-9ACA-F3576FC7FA1F}">
-  <dimension ref="B2:AE183"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383C4B93-F69E-4361-BEB8-AB7424396470}">
+  <dimension ref="B2:AE216"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:31" x14ac:dyDescent="0.45">
@@ -2200,16 +2464,16 @@
         <v>253</v>
       </c>
       <c r="AB4" t="s">
-        <v>483</v>
+        <v>571</v>
       </c>
       <c r="AC4" t="s">
-        <v>485</v>
+        <v>573</v>
       </c>
       <c r="AD4" t="s">
-        <v>486</v>
+        <v>574</v>
       </c>
       <c r="AE4" t="s">
-        <v>487</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.45">
@@ -2262,10 +2526,10 @@
         <v>314</v>
       </c>
       <c r="AA5" t="s">
-        <v>482</v>
+        <v>570</v>
       </c>
       <c r="AB5" t="s">
-        <v>484</v>
+        <v>572</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2274,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>488</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.45">
@@ -4171,7 +4435,7 @@
         <v>354</v>
       </c>
       <c r="W43" t="s">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="X43" t="s">
         <v>314</v>
@@ -4194,10 +4458,10 @@
         <v>92</v>
       </c>
       <c r="V44" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="W44" t="s">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="X44" t="s">
         <v>314</v>
@@ -4220,10 +4484,10 @@
         <v>92</v>
       </c>
       <c r="V45" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="W45" t="s">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="X45" t="s">
         <v>314</v>
@@ -4246,10 +4510,10 @@
         <v>92</v>
       </c>
       <c r="V46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="W46" t="s">
-        <v>357</v>
+        <v>302</v>
       </c>
       <c r="X46" t="s">
         <v>314</v>
@@ -4272,10 +4536,10 @@
         <v>92</v>
       </c>
       <c r="V47" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="W47" t="s">
-        <v>357</v>
+        <v>302</v>
       </c>
       <c r="X47" t="s">
         <v>314</v>
@@ -4298,10 +4562,10 @@
         <v>92</v>
       </c>
       <c r="V48" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="W48" t="s">
-        <v>357</v>
+        <v>302</v>
       </c>
       <c r="X48" t="s">
         <v>314</v>
@@ -4324,10 +4588,10 @@
         <v>92</v>
       </c>
       <c r="V49" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="W49" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="X49" t="s">
         <v>314</v>
@@ -4350,10 +4614,10 @@
         <v>92</v>
       </c>
       <c r="V50" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="W50" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="X50" t="s">
         <v>314</v>
@@ -4376,10 +4640,10 @@
         <v>92</v>
       </c>
       <c r="V51" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="W51" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="X51" t="s">
         <v>314</v>
@@ -4402,10 +4666,10 @@
         <v>92</v>
       </c>
       <c r="V52" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="W52" t="s">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="X52" t="s">
         <v>314</v>
@@ -4428,10 +4692,10 @@
         <v>92</v>
       </c>
       <c r="V53" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="W53" t="s">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="X53" t="s">
         <v>314</v>
@@ -4454,10 +4718,10 @@
         <v>92</v>
       </c>
       <c r="V54" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="W54" t="s">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="X54" t="s">
         <v>314</v>
@@ -4480,10 +4744,10 @@
         <v>92</v>
       </c>
       <c r="V55" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="W55" t="s">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="X55" t="s">
         <v>314</v>
@@ -4506,10 +4770,10 @@
         <v>92</v>
       </c>
       <c r="V56" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W56" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="X56" t="s">
         <v>314</v>
@@ -4532,10 +4796,10 @@
         <v>92</v>
       </c>
       <c r="V57" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="W57" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="X57" t="s">
         <v>314</v>
@@ -4558,10 +4822,10 @@
         <v>92</v>
       </c>
       <c r="V58" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="W58" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="X58" t="s">
         <v>314</v>
@@ -4584,10 +4848,10 @@
         <v>92</v>
       </c>
       <c r="V59" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="W59" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="X59" t="s">
         <v>314</v>
@@ -4610,10 +4874,10 @@
         <v>92</v>
       </c>
       <c r="V60" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="W60" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="X60" t="s">
         <v>314</v>
@@ -4636,10 +4900,10 @@
         <v>92</v>
       </c>
       <c r="V61" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="W61" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="X61" t="s">
         <v>314</v>
@@ -4662,10 +4926,10 @@
         <v>92</v>
       </c>
       <c r="V62" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="W62" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="X62" t="s">
         <v>314</v>
@@ -4688,10 +4952,10 @@
         <v>92</v>
       </c>
       <c r="V63" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="W63" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="X63" t="s">
         <v>314</v>
@@ -4714,10 +4978,10 @@
         <v>92</v>
       </c>
       <c r="V64" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="W64" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="X64" t="s">
         <v>314</v>
@@ -4740,10 +5004,10 @@
         <v>92</v>
       </c>
       <c r="V65" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="W65" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="X65" t="s">
         <v>314</v>
@@ -4766,10 +5030,10 @@
         <v>92</v>
       </c>
       <c r="V66" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="W66" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="X66" t="s">
         <v>314</v>
@@ -4792,10 +5056,10 @@
         <v>92</v>
       </c>
       <c r="V67" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="W67" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="X67" t="s">
         <v>314</v>
@@ -4818,10 +5082,10 @@
         <v>92</v>
       </c>
       <c r="V68" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="W68" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="X68" t="s">
         <v>314</v>
@@ -4844,10 +5108,10 @@
         <v>92</v>
       </c>
       <c r="V69" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="W69" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="X69" t="s">
         <v>314</v>
@@ -4870,10 +5134,10 @@
         <v>92</v>
       </c>
       <c r="V70" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="W70" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="X70" t="s">
         <v>314</v>
@@ -4896,10 +5160,10 @@
         <v>92</v>
       </c>
       <c r="V71" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="W71" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="X71" t="s">
         <v>314</v>
@@ -4922,10 +5186,10 @@
         <v>92</v>
       </c>
       <c r="V72" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="W72" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="X72" t="s">
         <v>314</v>
@@ -4948,10 +5212,10 @@
         <v>92</v>
       </c>
       <c r="V73" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="W73" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="X73" t="s">
         <v>314</v>
@@ -4974,10 +5238,10 @@
         <v>92</v>
       </c>
       <c r="V74" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="W74" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="X74" t="s">
         <v>314</v>
@@ -5000,10 +5264,10 @@
         <v>92</v>
       </c>
       <c r="V75" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="W75" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="X75" t="s">
         <v>314</v>
@@ -5026,10 +5290,10 @@
         <v>92</v>
       </c>
       <c r="V76" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="W76" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="X76" t="s">
         <v>314</v>
@@ -5052,10 +5316,10 @@
         <v>92</v>
       </c>
       <c r="V77" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="W77" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="X77" t="s">
         <v>314</v>
@@ -5078,10 +5342,10 @@
         <v>92</v>
       </c>
       <c r="V78" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="W78" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="X78" t="s">
         <v>314</v>
@@ -5104,10 +5368,10 @@
         <v>92</v>
       </c>
       <c r="V79" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="W79" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="X79" t="s">
         <v>314</v>
@@ -5130,10 +5394,10 @@
         <v>92</v>
       </c>
       <c r="V80" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="W80" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="X80" t="s">
         <v>314</v>
@@ -5156,10 +5420,10 @@
         <v>92</v>
       </c>
       <c r="V81" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="W81" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="X81" t="s">
         <v>314</v>
@@ -5182,10 +5446,10 @@
         <v>92</v>
       </c>
       <c r="V82" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="W82" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="X82" t="s">
         <v>314</v>
@@ -5208,10 +5472,10 @@
         <v>92</v>
       </c>
       <c r="V83" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="W83" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="X83" t="s">
         <v>314</v>
@@ -5234,10 +5498,10 @@
         <v>92</v>
       </c>
       <c r="V84" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="W84" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="X84" t="s">
         <v>314</v>
@@ -5260,10 +5524,10 @@
         <v>92</v>
       </c>
       <c r="V85" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="W85" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="X85" t="s">
         <v>314</v>
@@ -5286,10 +5550,10 @@
         <v>92</v>
       </c>
       <c r="V86" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="W86" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="X86" t="s">
         <v>314</v>
@@ -5312,10 +5576,10 @@
         <v>92</v>
       </c>
       <c r="V87" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="W87" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="X87" t="s">
         <v>314</v>
@@ -5338,10 +5602,10 @@
         <v>92</v>
       </c>
       <c r="V88" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="W88" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="X88" t="s">
         <v>314</v>
@@ -5364,10 +5628,10 @@
         <v>92</v>
       </c>
       <c r="V89" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="W89" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="X89" t="s">
         <v>314</v>
@@ -5390,10 +5654,10 @@
         <v>92</v>
       </c>
       <c r="V90" t="s">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="W90" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="X90" t="s">
         <v>314</v>
@@ -5416,10 +5680,10 @@
         <v>92</v>
       </c>
       <c r="V91" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="W91" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="X91" t="s">
         <v>314</v>
@@ -5442,10 +5706,10 @@
         <v>92</v>
       </c>
       <c r="V92" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="W92" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="X92" t="s">
         <v>314</v>
@@ -5468,10 +5732,10 @@
         <v>92</v>
       </c>
       <c r="V93" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="W93" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="X93" t="s">
         <v>314</v>
@@ -5494,10 +5758,10 @@
         <v>92</v>
       </c>
       <c r="V94" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="W94" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="X94" t="s">
         <v>314</v>
@@ -5520,10 +5784,10 @@
         <v>92</v>
       </c>
       <c r="V95" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="W95" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="X95" t="s">
         <v>314</v>
@@ -5546,10 +5810,10 @@
         <v>92</v>
       </c>
       <c r="V96" t="s">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="W96" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="X96" t="s">
         <v>314</v>
@@ -5572,10 +5836,10 @@
         <v>92</v>
       </c>
       <c r="V97" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="W97" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="X97" t="s">
         <v>314</v>
@@ -5598,10 +5862,10 @@
         <v>92</v>
       </c>
       <c r="V98" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="W98" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="X98" t="s">
         <v>314</v>
@@ -5624,10 +5888,10 @@
         <v>92</v>
       </c>
       <c r="V99" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="W99" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="X99" t="s">
         <v>314</v>
@@ -5650,10 +5914,10 @@
         <v>92</v>
       </c>
       <c r="V100" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="W100" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="X100" t="s">
         <v>314</v>
@@ -5676,10 +5940,10 @@
         <v>92</v>
       </c>
       <c r="V101" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="W101" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="X101" t="s">
         <v>314</v>
@@ -5702,10 +5966,10 @@
         <v>92</v>
       </c>
       <c r="V102" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="W102" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="X102" t="s">
         <v>314</v>
@@ -5728,10 +5992,10 @@
         <v>92</v>
       </c>
       <c r="V103" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="W103" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="X103" t="s">
         <v>314</v>
@@ -5754,10 +6018,10 @@
         <v>92</v>
       </c>
       <c r="V104" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="W104" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="X104" t="s">
         <v>314</v>
@@ -5780,10 +6044,10 @@
         <v>92</v>
       </c>
       <c r="V105" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="W105" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="X105" t="s">
         <v>314</v>
@@ -5806,10 +6070,10 @@
         <v>92</v>
       </c>
       <c r="V106" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="W106" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="X106" t="s">
         <v>314</v>
@@ -5832,10 +6096,10 @@
         <v>92</v>
       </c>
       <c r="V107" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="W107" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="X107" t="s">
         <v>314</v>
@@ -5858,10 +6122,10 @@
         <v>92</v>
       </c>
       <c r="V108" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="W108" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="X108" t="s">
         <v>314</v>
@@ -5884,10 +6148,10 @@
         <v>92</v>
       </c>
       <c r="V109" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="W109" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="X109" t="s">
         <v>314</v>
@@ -5910,10 +6174,10 @@
         <v>92</v>
       </c>
       <c r="V110" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="W110" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="X110" t="s">
         <v>314</v>
@@ -5936,10 +6200,10 @@
         <v>92</v>
       </c>
       <c r="V111" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="W111" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="X111" t="s">
         <v>314</v>
@@ -5962,10 +6226,10 @@
         <v>92</v>
       </c>
       <c r="V112" t="s">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="W112" t="s">
-        <v>313</v>
+        <v>440</v>
       </c>
       <c r="X112" t="s">
         <v>314</v>
@@ -5988,10 +6252,10 @@
         <v>92</v>
       </c>
       <c r="V113" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="W113" t="s">
-        <v>313</v>
+        <v>444</v>
       </c>
       <c r="X113" t="s">
         <v>314</v>
@@ -6014,10 +6278,10 @@
         <v>92</v>
       </c>
       <c r="V114" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
       <c r="W114" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="X114" t="s">
         <v>314</v>
@@ -6040,10 +6304,10 @@
         <v>92</v>
       </c>
       <c r="V115" t="s">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="W115" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="X115" t="s">
         <v>314</v>
@@ -6066,10 +6330,10 @@
         <v>92</v>
       </c>
       <c r="V116" t="s">
-        <v>404</v>
+        <v>447</v>
       </c>
       <c r="W116" t="s">
-        <v>310</v>
+        <v>448</v>
       </c>
       <c r="X116" t="s">
         <v>314</v>
@@ -6092,10 +6356,10 @@
         <v>92</v>
       </c>
       <c r="V117" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="W117" t="s">
-        <v>310</v>
+        <v>448</v>
       </c>
       <c r="X117" t="s">
         <v>314</v>
@@ -6118,10 +6382,10 @@
         <v>92</v>
       </c>
       <c r="V118" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="W118" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="X118" t="s">
         <v>314</v>
@@ -6144,10 +6408,10 @@
         <v>92</v>
       </c>
       <c r="V119" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="W119" t="s">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="X119" t="s">
         <v>314</v>
@@ -6170,10 +6434,10 @@
         <v>92</v>
       </c>
       <c r="V120" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="W120" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="X120" t="s">
         <v>314</v>
@@ -6196,10 +6460,10 @@
         <v>92</v>
       </c>
       <c r="V121" t="s">
-        <v>411</v>
+        <v>454</v>
       </c>
       <c r="W121" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="X121" t="s">
         <v>314</v>
@@ -6222,10 +6486,10 @@
         <v>92</v>
       </c>
       <c r="V122" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="W122" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="X122" t="s">
         <v>314</v>
@@ -6248,10 +6512,10 @@
         <v>92</v>
       </c>
       <c r="V123" t="s">
-        <v>414</v>
+        <v>457</v>
       </c>
       <c r="W123" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="X123" t="s">
         <v>314</v>
@@ -6274,10 +6538,10 @@
         <v>92</v>
       </c>
       <c r="V124" t="s">
-        <v>415</v>
+        <v>458</v>
       </c>
       <c r="W124" t="s">
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="X124" t="s">
         <v>314</v>
@@ -6300,10 +6564,10 @@
         <v>92</v>
       </c>
       <c r="V125" t="s">
-        <v>417</v>
+        <v>459</v>
       </c>
       <c r="W125" t="s">
-        <v>416</v>
+        <v>313</v>
       </c>
       <c r="X125" t="s">
         <v>314</v>
@@ -6326,10 +6590,10 @@
         <v>92</v>
       </c>
       <c r="V126" t="s">
-        <v>418</v>
+        <v>460</v>
       </c>
       <c r="W126" t="s">
-        <v>419</v>
+        <v>313</v>
       </c>
       <c r="X126" t="s">
         <v>314</v>
@@ -6352,10 +6616,10 @@
         <v>92</v>
       </c>
       <c r="V127" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="W127" t="s">
-        <v>419</v>
+        <v>328</v>
       </c>
       <c r="X127" t="s">
         <v>314</v>
@@ -6378,10 +6642,10 @@
         <v>92</v>
       </c>
       <c r="V128" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="W128" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="X128" t="s">
         <v>314</v>
@@ -6404,10 +6668,10 @@
         <v>92</v>
       </c>
       <c r="V129" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="W129" t="s">
-        <v>422</v>
+        <v>310</v>
       </c>
       <c r="X129" t="s">
         <v>314</v>
@@ -6430,10 +6694,10 @@
         <v>92</v>
       </c>
       <c r="V130" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="W130" t="s">
-        <v>425</v>
+        <v>310</v>
       </c>
       <c r="X130" t="s">
         <v>314</v>
@@ -6456,10 +6720,10 @@
         <v>92</v>
       </c>
       <c r="V131" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="W131" t="s">
-        <v>425</v>
+        <v>302</v>
       </c>
       <c r="X131" t="s">
         <v>314</v>
@@ -6482,10 +6746,10 @@
         <v>92</v>
       </c>
       <c r="V132" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="W132" t="s">
-        <v>428</v>
+        <v>302</v>
       </c>
       <c r="X132" t="s">
         <v>314</v>
@@ -6508,10 +6772,10 @@
         <v>92</v>
       </c>
       <c r="V133" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="W133" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="X133" t="s">
         <v>314</v>
@@ -6534,10 +6798,10 @@
         <v>92</v>
       </c>
       <c r="V134" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="W134" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="X134" t="s">
         <v>314</v>
@@ -6560,10 +6824,10 @@
         <v>92</v>
       </c>
       <c r="V135" t="s">
-        <v>432</v>
+        <v>470</v>
       </c>
       <c r="W135" t="s">
-        <v>431</v>
+        <v>471</v>
       </c>
       <c r="X135" t="s">
         <v>314</v>
@@ -6586,10 +6850,10 @@
         <v>92</v>
       </c>
       <c r="V136" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="W136" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="X136" t="s">
         <v>314</v>
@@ -6612,10 +6876,10 @@
         <v>92</v>
       </c>
       <c r="V137" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="W137" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="X137" t="s">
         <v>314</v>
@@ -6638,10 +6902,10 @@
         <v>92</v>
       </c>
       <c r="V138" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="W138" t="s">
-        <v>355</v>
+        <v>474</v>
       </c>
       <c r="X138" t="s">
         <v>314</v>
@@ -6664,10 +6928,10 @@
         <v>92</v>
       </c>
       <c r="V139" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
       <c r="W139" t="s">
-        <v>355</v>
+        <v>477</v>
       </c>
       <c r="X139" t="s">
         <v>314</v>
@@ -6690,10 +6954,10 @@
         <v>92</v>
       </c>
       <c r="V140" t="s">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="W140" t="s">
-        <v>357</v>
+        <v>477</v>
       </c>
       <c r="X140" t="s">
         <v>314</v>
@@ -6716,10 +6980,10 @@
         <v>92</v>
       </c>
       <c r="V141" t="s">
-        <v>439</v>
+        <v>479</v>
       </c>
       <c r="W141" t="s">
-        <v>357</v>
+        <v>424</v>
       </c>
       <c r="X141" t="s">
         <v>314</v>
@@ -6742,10 +7006,10 @@
         <v>92</v>
       </c>
       <c r="V142" t="s">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="W142" t="s">
-        <v>359</v>
+        <v>424</v>
       </c>
       <c r="X142" t="s">
         <v>314</v>
@@ -6768,10 +7032,10 @@
         <v>92</v>
       </c>
       <c r="V143" t="s">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="W143" t="s">
-        <v>359</v>
+        <v>482</v>
       </c>
       <c r="X143" t="s">
         <v>314</v>
@@ -6794,10 +7058,10 @@
         <v>92</v>
       </c>
       <c r="V144" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="W144" t="s">
-        <v>361</v>
+        <v>482</v>
       </c>
       <c r="X144" t="s">
         <v>314</v>
@@ -6820,10 +7084,10 @@
         <v>92</v>
       </c>
       <c r="V145" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="W145" t="s">
-        <v>361</v>
+        <v>485</v>
       </c>
       <c r="X145" t="s">
         <v>314</v>
@@ -6846,10 +7110,10 @@
         <v>92</v>
       </c>
       <c r="V146" t="s">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="W146" t="s">
-        <v>363</v>
+        <v>485</v>
       </c>
       <c r="X146" t="s">
         <v>314</v>
@@ -6872,10 +7136,10 @@
         <v>92</v>
       </c>
       <c r="V147" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="W147" t="s">
-        <v>363</v>
+        <v>488</v>
       </c>
       <c r="X147" t="s">
         <v>314</v>
@@ -6898,10 +7162,10 @@
         <v>92</v>
       </c>
       <c r="V148" t="s">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="W148" t="s">
-        <v>365</v>
+        <v>488</v>
       </c>
       <c r="X148" t="s">
         <v>314</v>
@@ -6924,10 +7188,10 @@
         <v>92</v>
       </c>
       <c r="V149" t="s">
-        <v>447</v>
+        <v>490</v>
       </c>
       <c r="W149" t="s">
-        <v>365</v>
+        <v>491</v>
       </c>
       <c r="X149" t="s">
         <v>314</v>
@@ -6950,10 +7214,10 @@
         <v>92</v>
       </c>
       <c r="V150" t="s">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="W150" t="s">
-        <v>367</v>
+        <v>491</v>
       </c>
       <c r="X150" t="s">
         <v>314</v>
@@ -6976,10 +7240,10 @@
         <v>92</v>
       </c>
       <c r="V151" t="s">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="W151" t="s">
-        <v>367</v>
+        <v>494</v>
       </c>
       <c r="X151" t="s">
         <v>314</v>
@@ -7002,10 +7266,10 @@
         <v>92</v>
       </c>
       <c r="V152" t="s">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="W152" t="s">
-        <v>369</v>
+        <v>494</v>
       </c>
       <c r="X152" t="s">
         <v>314</v>
@@ -7028,10 +7292,10 @@
         <v>92</v>
       </c>
       <c r="V153" t="s">
-        <v>451</v>
+        <v>496</v>
       </c>
       <c r="W153" t="s">
-        <v>369</v>
+        <v>497</v>
       </c>
       <c r="X153" t="s">
         <v>314</v>
@@ -7054,10 +7318,10 @@
         <v>92</v>
       </c>
       <c r="V154" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="W154" t="s">
-        <v>371</v>
+        <v>497</v>
       </c>
       <c r="X154" t="s">
         <v>314</v>
@@ -7080,10 +7344,10 @@
         <v>92</v>
       </c>
       <c r="V155" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
       <c r="W155" t="s">
-        <v>371</v>
+        <v>500</v>
       </c>
       <c r="X155" t="s">
         <v>314</v>
@@ -7106,10 +7370,10 @@
         <v>92</v>
       </c>
       <c r="V156" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
       <c r="W156" t="s">
-        <v>373</v>
+        <v>500</v>
       </c>
       <c r="X156" t="s">
         <v>314</v>
@@ -7132,10 +7396,10 @@
         <v>92</v>
       </c>
       <c r="V157" t="s">
-        <v>455</v>
+        <v>502</v>
       </c>
       <c r="W157" t="s">
-        <v>373</v>
+        <v>503</v>
       </c>
       <c r="X157" t="s">
         <v>314</v>
@@ -7158,10 +7422,10 @@
         <v>92</v>
       </c>
       <c r="V158" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="W158" t="s">
-        <v>375</v>
+        <v>503</v>
       </c>
       <c r="X158" t="s">
         <v>314</v>
@@ -7184,10 +7448,10 @@
         <v>92</v>
       </c>
       <c r="V159" t="s">
-        <v>457</v>
+        <v>505</v>
       </c>
       <c r="W159" t="s">
-        <v>375</v>
+        <v>506</v>
       </c>
       <c r="X159" t="s">
         <v>314</v>
@@ -7198,10 +7462,10 @@
         <v>92</v>
       </c>
       <c r="V160" t="s">
-        <v>458</v>
+        <v>507</v>
       </c>
       <c r="W160" t="s">
-        <v>377</v>
+        <v>506</v>
       </c>
       <c r="X160" t="s">
         <v>314</v>
@@ -7212,10 +7476,10 @@
         <v>92</v>
       </c>
       <c r="V161" t="s">
-        <v>459</v>
+        <v>508</v>
       </c>
       <c r="W161" t="s">
-        <v>377</v>
+        <v>509</v>
       </c>
       <c r="X161" t="s">
         <v>314</v>
@@ -7226,10 +7490,10 @@
         <v>92</v>
       </c>
       <c r="V162" t="s">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="W162" t="s">
-        <v>379</v>
+        <v>509</v>
       </c>
       <c r="X162" t="s">
         <v>314</v>
@@ -7240,10 +7504,10 @@
         <v>92</v>
       </c>
       <c r="V163" t="s">
-        <v>461</v>
+        <v>511</v>
       </c>
       <c r="W163" t="s">
-        <v>379</v>
+        <v>512</v>
       </c>
       <c r="X163" t="s">
         <v>314</v>
@@ -7254,10 +7518,10 @@
         <v>92</v>
       </c>
       <c r="V164" t="s">
-        <v>462</v>
+        <v>513</v>
       </c>
       <c r="W164" t="s">
-        <v>381</v>
+        <v>512</v>
       </c>
       <c r="X164" t="s">
         <v>314</v>
@@ -7268,10 +7532,10 @@
         <v>92</v>
       </c>
       <c r="V165" t="s">
-        <v>463</v>
+        <v>514</v>
       </c>
       <c r="W165" t="s">
-        <v>381</v>
+        <v>515</v>
       </c>
       <c r="X165" t="s">
         <v>314</v>
@@ -7282,10 +7546,10 @@
         <v>92</v>
       </c>
       <c r="V166" t="s">
-        <v>464</v>
+        <v>516</v>
       </c>
       <c r="W166" t="s">
-        <v>383</v>
+        <v>515</v>
       </c>
       <c r="X166" t="s">
         <v>314</v>
@@ -7296,10 +7560,10 @@
         <v>92</v>
       </c>
       <c r="V167" t="s">
-        <v>465</v>
+        <v>517</v>
       </c>
       <c r="W167" t="s">
-        <v>383</v>
+        <v>518</v>
       </c>
       <c r="X167" t="s">
         <v>314</v>
@@ -7310,10 +7574,10 @@
         <v>92</v>
       </c>
       <c r="V168" t="s">
-        <v>466</v>
+        <v>519</v>
       </c>
       <c r="W168" t="s">
-        <v>385</v>
+        <v>518</v>
       </c>
       <c r="X168" t="s">
         <v>314</v>
@@ -7324,10 +7588,10 @@
         <v>92</v>
       </c>
       <c r="V169" t="s">
-        <v>467</v>
+        <v>520</v>
       </c>
       <c r="W169" t="s">
-        <v>385</v>
+        <v>521</v>
       </c>
       <c r="X169" t="s">
         <v>314</v>
@@ -7338,10 +7602,10 @@
         <v>92</v>
       </c>
       <c r="V170" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="W170" t="s">
-        <v>387</v>
+        <v>521</v>
       </c>
       <c r="X170" t="s">
         <v>314</v>
@@ -7352,10 +7616,10 @@
         <v>92</v>
       </c>
       <c r="V171" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="W171" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="X171" t="s">
         <v>314</v>
@@ -7366,10 +7630,10 @@
         <v>92</v>
       </c>
       <c r="V172" t="s">
-        <v>470</v>
+        <v>524</v>
       </c>
       <c r="W172" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="X172" t="s">
         <v>314</v>
@@ -7380,10 +7644,10 @@
         <v>92</v>
       </c>
       <c r="V173" t="s">
-        <v>471</v>
+        <v>525</v>
       </c>
       <c r="W173" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="X173" t="s">
         <v>314</v>
@@ -7394,10 +7658,10 @@
         <v>92</v>
       </c>
       <c r="V174" t="s">
-        <v>472</v>
+        <v>526</v>
       </c>
       <c r="W174" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="X174" t="s">
         <v>314</v>
@@ -7408,10 +7672,10 @@
         <v>92</v>
       </c>
       <c r="V175" t="s">
-        <v>473</v>
+        <v>527</v>
       </c>
       <c r="W175" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="X175" t="s">
         <v>314</v>
@@ -7422,10 +7686,10 @@
         <v>92</v>
       </c>
       <c r="V176" t="s">
-        <v>474</v>
+        <v>528</v>
       </c>
       <c r="W176" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="X176" t="s">
         <v>314</v>
@@ -7436,10 +7700,10 @@
         <v>92</v>
       </c>
       <c r="V177" t="s">
-        <v>475</v>
+        <v>529</v>
       </c>
       <c r="W177" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="X177" t="s">
         <v>314</v>
@@ -7450,10 +7714,10 @@
         <v>92</v>
       </c>
       <c r="V178" t="s">
-        <v>476</v>
+        <v>530</v>
       </c>
       <c r="W178" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="X178" t="s">
         <v>314</v>
@@ -7464,10 +7728,10 @@
         <v>92</v>
       </c>
       <c r="V179" t="s">
-        <v>477</v>
+        <v>531</v>
       </c>
       <c r="W179" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="X179" t="s">
         <v>314</v>
@@ -7478,10 +7742,10 @@
         <v>92</v>
       </c>
       <c r="V180" t="s">
-        <v>478</v>
+        <v>532</v>
       </c>
       <c r="W180" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="X180" t="s">
         <v>314</v>
@@ -7492,10 +7756,10 @@
         <v>92</v>
       </c>
       <c r="V181" t="s">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="W181" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="X181" t="s">
         <v>314</v>
@@ -7506,10 +7770,10 @@
         <v>92</v>
       </c>
       <c r="V182" t="s">
-        <v>480</v>
+        <v>534</v>
       </c>
       <c r="W182" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="X182" t="s">
         <v>314</v>
@@ -7520,12 +7784,474 @@
         <v>92</v>
       </c>
       <c r="V183" t="s">
-        <v>481</v>
+        <v>535</v>
       </c>
       <c r="W183" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="X183" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="184" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U184" t="s">
+        <v>92</v>
+      </c>
+      <c r="V184" t="s">
+        <v>536</v>
+      </c>
+      <c r="W184" t="s">
+        <v>392</v>
+      </c>
+      <c r="X184" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="185" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U185" t="s">
+        <v>92</v>
+      </c>
+      <c r="V185" t="s">
+        <v>537</v>
+      </c>
+      <c r="W185" t="s">
+        <v>396</v>
+      </c>
+      <c r="X185" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="186" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U186" t="s">
+        <v>92</v>
+      </c>
+      <c r="V186" t="s">
+        <v>538</v>
+      </c>
+      <c r="W186" t="s">
+        <v>396</v>
+      </c>
+      <c r="X186" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="187" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U187" t="s">
+        <v>92</v>
+      </c>
+      <c r="V187" t="s">
+        <v>539</v>
+      </c>
+      <c r="W187" t="s">
+        <v>400</v>
+      </c>
+      <c r="X187" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="188" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U188" t="s">
+        <v>92</v>
+      </c>
+      <c r="V188" t="s">
+        <v>540</v>
+      </c>
+      <c r="W188" t="s">
+        <v>400</v>
+      </c>
+      <c r="X188" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="189" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U189" t="s">
+        <v>92</v>
+      </c>
+      <c r="V189" t="s">
+        <v>541</v>
+      </c>
+      <c r="W189" t="s">
+        <v>404</v>
+      </c>
+      <c r="X189" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="190" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U190" t="s">
+        <v>92</v>
+      </c>
+      <c r="V190" t="s">
+        <v>542</v>
+      </c>
+      <c r="W190" t="s">
+        <v>404</v>
+      </c>
+      <c r="X190" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="191" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U191" t="s">
+        <v>92</v>
+      </c>
+      <c r="V191" t="s">
+        <v>543</v>
+      </c>
+      <c r="W191" t="s">
+        <v>408</v>
+      </c>
+      <c r="X191" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="192" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U192" t="s">
+        <v>92</v>
+      </c>
+      <c r="V192" t="s">
+        <v>544</v>
+      </c>
+      <c r="W192" t="s">
+        <v>408</v>
+      </c>
+      <c r="X192" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="193" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U193" t="s">
+        <v>92</v>
+      </c>
+      <c r="V193" t="s">
+        <v>545</v>
+      </c>
+      <c r="W193" t="s">
+        <v>412</v>
+      </c>
+      <c r="X193" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="194" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U194" t="s">
+        <v>92</v>
+      </c>
+      <c r="V194" t="s">
+        <v>546</v>
+      </c>
+      <c r="W194" t="s">
+        <v>412</v>
+      </c>
+      <c r="X194" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="195" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U195" t="s">
+        <v>92</v>
+      </c>
+      <c r="V195" t="s">
+        <v>547</v>
+      </c>
+      <c r="W195" t="s">
+        <v>416</v>
+      </c>
+      <c r="X195" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="196" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U196" t="s">
+        <v>92</v>
+      </c>
+      <c r="V196" t="s">
+        <v>548</v>
+      </c>
+      <c r="W196" t="s">
+        <v>416</v>
+      </c>
+      <c r="X196" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="197" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U197" t="s">
+        <v>92</v>
+      </c>
+      <c r="V197" t="s">
+        <v>549</v>
+      </c>
+      <c r="W197" t="s">
+        <v>420</v>
+      </c>
+      <c r="X197" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="198" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U198" t="s">
+        <v>92</v>
+      </c>
+      <c r="V198" t="s">
+        <v>550</v>
+      </c>
+      <c r="W198" t="s">
+        <v>420</v>
+      </c>
+      <c r="X198" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="199" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U199" t="s">
+        <v>92</v>
+      </c>
+      <c r="V199" t="s">
+        <v>551</v>
+      </c>
+      <c r="W199" t="s">
+        <v>428</v>
+      </c>
+      <c r="X199" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="200" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U200" t="s">
+        <v>92</v>
+      </c>
+      <c r="V200" t="s">
+        <v>552</v>
+      </c>
+      <c r="W200" t="s">
+        <v>428</v>
+      </c>
+      <c r="X200" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="201" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U201" t="s">
+        <v>92</v>
+      </c>
+      <c r="V201" t="s">
+        <v>553</v>
+      </c>
+      <c r="W201" t="s">
+        <v>432</v>
+      </c>
+      <c r="X201" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="202" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U202" t="s">
+        <v>92</v>
+      </c>
+      <c r="V202" t="s">
+        <v>554</v>
+      </c>
+      <c r="W202" t="s">
+        <v>432</v>
+      </c>
+      <c r="X202" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="203" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U203" t="s">
+        <v>92</v>
+      </c>
+      <c r="V203" t="s">
+        <v>555</v>
+      </c>
+      <c r="W203" t="s">
+        <v>436</v>
+      </c>
+      <c r="X203" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="204" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U204" t="s">
+        <v>92</v>
+      </c>
+      <c r="V204" t="s">
+        <v>556</v>
+      </c>
+      <c r="W204" t="s">
+        <v>436</v>
+      </c>
+      <c r="X204" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="205" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U205" t="s">
+        <v>92</v>
+      </c>
+      <c r="V205" t="s">
+        <v>557</v>
+      </c>
+      <c r="W205" t="s">
+        <v>440</v>
+      </c>
+      <c r="X205" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="206" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U206" t="s">
+        <v>92</v>
+      </c>
+      <c r="V206" t="s">
+        <v>558</v>
+      </c>
+      <c r="W206" t="s">
+        <v>440</v>
+      </c>
+      <c r="X206" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="207" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U207" t="s">
+        <v>92</v>
+      </c>
+      <c r="V207" t="s">
+        <v>559</v>
+      </c>
+      <c r="W207" t="s">
+        <v>444</v>
+      </c>
+      <c r="X207" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="208" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U208" t="s">
+        <v>92</v>
+      </c>
+      <c r="V208" t="s">
+        <v>560</v>
+      </c>
+      <c r="W208" t="s">
+        <v>444</v>
+      </c>
+      <c r="X208" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="209" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U209" t="s">
+        <v>92</v>
+      </c>
+      <c r="V209" t="s">
+        <v>561</v>
+      </c>
+      <c r="W209" t="s">
+        <v>448</v>
+      </c>
+      <c r="X209" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="210" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U210" t="s">
+        <v>92</v>
+      </c>
+      <c r="V210" t="s">
+        <v>562</v>
+      </c>
+      <c r="W210" t="s">
+        <v>448</v>
+      </c>
+      <c r="X210" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="211" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U211" t="s">
+        <v>92</v>
+      </c>
+      <c r="V211" t="s">
+        <v>563</v>
+      </c>
+      <c r="W211" t="s">
+        <v>452</v>
+      </c>
+      <c r="X211" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="212" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U212" t="s">
+        <v>92</v>
+      </c>
+      <c r="V212" t="s">
+        <v>564</v>
+      </c>
+      <c r="W212" t="s">
+        <v>452</v>
+      </c>
+      <c r="X212" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="213" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U213" t="s">
+        <v>92</v>
+      </c>
+      <c r="V213" t="s">
+        <v>565</v>
+      </c>
+      <c r="W213" t="s">
+        <v>456</v>
+      </c>
+      <c r="X213" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="214" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U214" t="s">
+        <v>92</v>
+      </c>
+      <c r="V214" t="s">
+        <v>566</v>
+      </c>
+      <c r="W214" t="s">
+        <v>456</v>
+      </c>
+      <c r="X214" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="215" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U215" t="s">
+        <v>92</v>
+      </c>
+      <c r="V215" t="s">
+        <v>567</v>
+      </c>
+      <c r="W215" t="s">
+        <v>568</v>
+      </c>
+      <c r="X215" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="216" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U216" t="s">
+        <v>92</v>
+      </c>
+      <c r="V216" t="s">
+        <v>569</v>
+      </c>
+      <c r="W216" t="s">
+        <v>568</v>
+      </c>
+      <c r="X216" t="s">
         <v>314</v>
       </c>
     </row>

--- a/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C8D183F-56A1-4511-811C-249FDB407B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AF7D9F3-0C5E-43A5-8A9B-7590B5814D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2340,7 +2340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{383C4B93-F69E-4361-BEB8-AB7424396470}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37A0932-2571-42A8-A392-6BC0D2DAC0CD}">
   <dimension ref="B2:AE216"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
